--- a/ZonasEscolares/excels/LIMA-LIMA-SAN_JUAN_DE_MIRAFLORES.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SAN_JUAN_DE_MIRAFLORES.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-SAN_JUAN_DE_MIRAFLORES.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SAN_JUAN_DE_MIRAFLORES.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>LEONARD EULER II</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.16352</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-76.97335</v>
-      </c>
-      <c r="I2" t="n">
-        <v>418</v>
-      </c>
-      <c r="J2" t="n">
-        <v>23</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.16352</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-76.97335</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>CRISTO SEMBRADOR</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.13875</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.96307</v>
-      </c>
-      <c r="I3" t="n">
-        <v>314</v>
-      </c>
-      <c r="J3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.13875</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.96307</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>46 MI JARDIN DE AMOR</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.15124</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.97360999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>325</v>
-      </c>
-      <c r="J4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.15124</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.97361</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>56 MI DULCE HOGAR</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.15342</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.96783000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>300</v>
-      </c>
-      <c r="J5" t="n">
-        <v>13</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.15342</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.96783</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>66 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.14809</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.97192</v>
-      </c>
-      <c r="I6" t="n">
-        <v>368</v>
-      </c>
-      <c r="J6" t="n">
-        <v>16</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.14809</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.97192</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>513 NIÑOS DE MARIA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.16988</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.97503</v>
-      </c>
-      <c r="I7" t="n">
-        <v>268</v>
-      </c>
-      <c r="J7" t="n">
-        <v>13</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.16988</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.97503</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>514 EL CARMEN</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.16368</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.97778</v>
-      </c>
-      <c r="I8" t="n">
-        <v>421</v>
-      </c>
-      <c r="J8" t="n">
-        <v>17</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.16368</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.97778</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>530 VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.15953</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.96722</v>
-      </c>
-      <c r="I9" t="n">
-        <v>514</v>
-      </c>
-      <c r="J9" t="n">
-        <v>21</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.15953</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.96722</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>537 LOS LAURELES</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.14733</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.96239</v>
-      </c>
-      <c r="I10" t="n">
-        <v>221</v>
-      </c>
-      <c r="J10" t="n">
-        <v>10</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.14733</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.96239</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>JESUS NIÑO</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.16629</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.97278</v>
-      </c>
-      <c r="I11" t="n">
-        <v>453</v>
-      </c>
-      <c r="J11" t="n">
-        <v>17</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.16629</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.97278</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>541 DIVINO NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.13875</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-76.97184</v>
-      </c>
-      <c r="I12" t="n">
-        <v>343</v>
-      </c>
-      <c r="J12" t="n">
-        <v>15</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.13875</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-76.97184</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>547 JESUS PODEROSO</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.14829</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.98153000000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>344</v>
-      </c>
-      <c r="J13" t="n">
-        <v>18</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.14829</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.98153</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>551</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.13602</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.96065</v>
-      </c>
-      <c r="I14" t="n">
-        <v>269</v>
-      </c>
-      <c r="J14" t="n">
-        <v>12</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.13602</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.96065</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>559 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.17768</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.97801</v>
-      </c>
-      <c r="I15" t="n">
-        <v>204</v>
-      </c>
-      <c r="J15" t="n">
-        <v>9</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.17768</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.97801</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>623 / 7101</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.18447</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-76.97897</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1067</v>
-      </c>
-      <c r="J16" t="n">
-        <v>52</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.18447</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-76.97897</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1067</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>627 / 7212</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.17348</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.96406</v>
-      </c>
-      <c r="I17" t="n">
-        <v>468</v>
-      </c>
-      <c r="J17" t="n">
-        <v>20</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.17348</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.96406</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>629-6034 CESAR CARBONEL RODRIGUEZ</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.14525</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-76.9757</v>
-      </c>
-      <c r="I18" t="n">
-        <v>674</v>
-      </c>
-      <c r="J18" t="n">
-        <v>33</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.14525</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-76.9757</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>630 JUAN PABLO II</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.1394</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.95698</v>
-      </c>
-      <c r="I19" t="n">
-        <v>285</v>
-      </c>
-      <c r="J19" t="n">
-        <v>16</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.1394</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.95698</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>7219 ARISTOTELES</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.18595</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-76.95748</v>
-      </c>
-      <c r="I20" t="n">
-        <v>245</v>
-      </c>
-      <c r="J20" t="n">
-        <v>12</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.18595</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-76.95748</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>635 EL UNIVERSO</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.18626</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-76.95811</v>
-      </c>
-      <c r="I21" t="n">
-        <v>238</v>
-      </c>
-      <c r="J21" t="n">
-        <v>11</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.18626</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-76.95811</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>637 VALLE SHARON</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.17238</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-76.97072</v>
-      </c>
-      <c r="I22" t="n">
-        <v>447</v>
-      </c>
-      <c r="J22" t="n">
-        <v>20</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.17238</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-76.97072</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>638 PAMPAS DE SAN JUAN</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.1668</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-76.96566</v>
-      </c>
-      <c r="I23" t="n">
-        <v>245</v>
-      </c>
-      <c r="J23" t="n">
-        <v>12</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.1668</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-76.96566</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>7223 MIGUEL COLINA MARIE</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.15372</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-76.97969999999999</v>
-      </c>
-      <c r="I24" t="n">
-        <v>290</v>
-      </c>
-      <c r="J24" t="n">
-        <v>11</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.15372</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-76.9797</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>652 12 VIRGEN DEL BUEN PASO</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.14156</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-76.96250000000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>335</v>
-      </c>
-      <c r="J25" t="n">
-        <v>16</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.14156</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-76.9625</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>652 13 LOS TREBOLITOS</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-12.17753</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-76.96366999999999</v>
-      </c>
-      <c r="I26" t="n">
-        <v>193</v>
-      </c>
-      <c r="J26" t="n">
-        <v>9</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-12.17753</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-76.96367</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>652 19 HORACIO ZEBALLOS GAMEZ / 7227 HORACIO ZEBALLOS GAMEZ</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-12.1408</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-76.97873</v>
-      </c>
-      <c r="I27" t="n">
-        <v>442</v>
-      </c>
-      <c r="J27" t="n">
-        <v>23</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-12.1408</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-76.97873</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>652 27 LA MERCED DE LIMA / 7229 LA MERCED DE LIMA</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-12.18287</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-76.95871</v>
-      </c>
-      <c r="I28" t="n">
-        <v>276</v>
-      </c>
-      <c r="J28" t="n">
-        <v>12</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-12.18287</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-76.95871</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>6037 INCA PACHACUTEC</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-12.15624</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-76.96192000000001</v>
-      </c>
-      <c r="I29" t="n">
-        <v>226</v>
-      </c>
-      <c r="J29" t="n">
-        <v>11</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-12.15624</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-76.96192</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>6037 INCA PACHACUTEC</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-12.15682</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-76.964</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1059</v>
-      </c>
-      <c r="J30" t="n">
-        <v>56</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-12.15682</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-76.964</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>6041</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-12.1444</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-76.97127</v>
-      </c>
-      <c r="I31" t="n">
-        <v>949</v>
-      </c>
-      <c r="J31" t="n">
-        <v>46</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-12.1444</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-76.97127</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>6045 DOLORES CAVERO DE GRAU</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-12.15338</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-76.96729000000001</v>
-      </c>
-      <c r="I32" t="n">
-        <v>827</v>
-      </c>
-      <c r="J32" t="n">
-        <v>50</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-12.15338</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-76.96729</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>6046</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-12.14849</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-76.97235999999999</v>
-      </c>
-      <c r="I33" t="n">
-        <v>873</v>
-      </c>
-      <c r="J33" t="n">
-        <v>40</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-12.14849</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-76.97236</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>6078</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-12.15807</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-76.96832000000001</v>
-      </c>
-      <c r="I34" t="n">
-        <v>733</v>
-      </c>
-      <c r="J34" t="n">
-        <v>29</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-12.15807</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-76.96832</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>6089 JORGE BASADRE GROHMANN</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-12.14668</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-76.96287</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1097</v>
-      </c>
-      <c r="J35" t="n">
-        <v>57</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-12.14668</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-76.96287</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1097</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>6096 ANTONIO RAIMONDI</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-12.16712</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-76.96474000000001</v>
-      </c>
-      <c r="I36" t="n">
-        <v>797</v>
-      </c>
-      <c r="J36" t="n">
-        <v>37</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-12.16712</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-76.96474</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>797</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>6151 SAN LUIS GONZAGA</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-12.13945</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-76.97141000000001</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1329</v>
-      </c>
-      <c r="J37" t="n">
-        <v>69</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-12.13945</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-76.97141</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>7035</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-12.13536</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-76.95962</v>
-      </c>
-      <c r="I38" t="n">
-        <v>2001</v>
-      </c>
-      <c r="J38" t="n">
-        <v>100</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-12.13536</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-76.95962</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>7041 VIRGEN DE LA MERCED</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-12.16793</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-76.95869</v>
-      </c>
-      <c r="I39" t="n">
-        <v>746</v>
-      </c>
-      <c r="J39" t="n">
-        <v>28</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-12.16793</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-76.95869</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>7059 JOSE ANTONIO ENCINAS FRANCO</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-12.14751</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-76.96545999999999</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1323</v>
-      </c>
-      <c r="J40" t="n">
-        <v>59</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-12.14751</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-76.96546</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>7060 ANDRES AVELINO CACERES</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-12.15274</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-76.96267</v>
-      </c>
-      <c r="I41" t="n">
-        <v>432</v>
-      </c>
-      <c r="J41" t="n">
-        <v>23</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-12.15274</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-76.96267</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>7061 LOS HEROES DE SAN JUAN</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-12.15593</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-76.97544000000001</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1282</v>
-      </c>
-      <c r="J42" t="n">
-        <v>59</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-12.15593</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-76.97544</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>7062 NACIONES UNIDAS</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-12.15619</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-76.97483</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1651</v>
-      </c>
-      <c r="J43" t="n">
-        <v>84</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-12.15619</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-76.97483</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1651</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>7063 ANDRES AVELINO CACERES</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-12.16747</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-76.97414999999999</v>
-      </c>
-      <c r="I44" t="n">
-        <v>668</v>
-      </c>
-      <c r="J44" t="n">
-        <v>28</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-12.16747</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-76.97415</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>7067 TORIBIO SEMINARIO</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-12.15079</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-76.97775</v>
-      </c>
-      <c r="I45" t="n">
-        <v>606</v>
-      </c>
-      <c r="J45" t="n">
-        <v>38</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-12.15079</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-76.97775</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>7069 CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-12.15099</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-76.97448</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1516</v>
-      </c>
-      <c r="J46" t="n">
-        <v>74</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-12.15099</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-76.97448</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1516</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>7070 DRA. MARIA REICHE GROSSE NEUMAN</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-12.16776</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-76.97257999999999</v>
-      </c>
-      <c r="I47" t="n">
-        <v>1294</v>
-      </c>
-      <c r="J47" t="n">
-        <v>51</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-12.16776</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-76.97258</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>7074 LA INMACULADA</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-12.137</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-76.96823999999999</v>
-      </c>
-      <c r="I48" t="n">
-        <v>762</v>
-      </c>
-      <c r="J48" t="n">
-        <v>46</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-12.137</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-76.96824</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>7081 JOSE MARIA ARGUEDAS A</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-12.17933</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-76.97971</v>
-      </c>
-      <c r="I49" t="n">
-        <v>1288</v>
-      </c>
-      <c r="J49" t="n">
-        <v>60</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-12.17933</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-76.97971</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>7082 JUAN DE ESPINOSA MEDRANO</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-12.13264</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-76.96277000000001</v>
-      </c>
-      <c r="I50" t="n">
-        <v>784</v>
-      </c>
-      <c r="J50" t="n">
-        <v>39</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-12.13264</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-76.96277</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>7087 EL NAZARENO</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-12.13769</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-76.95632999999999</v>
-      </c>
-      <c r="I51" t="n">
-        <v>896</v>
-      </c>
-      <c r="J51" t="n">
-        <v>50</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-12.13769</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-76.95633</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>7099 HECTOR PRETELL / 7099 HECTOR PRETELL CARBONELL</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-12.17726</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-76.96907</v>
-      </c>
-      <c r="I52" t="n">
-        <v>646</v>
-      </c>
-      <c r="J52" t="n">
-        <v>30</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-12.17726</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-76.96907</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>7100 REPUBLICA ALEMANA</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-12.18017</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-76.95865999999999</v>
-      </c>
-      <c r="I53" t="n">
-        <v>792</v>
-      </c>
-      <c r="J53" t="n">
-        <v>45</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-12.18017</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-76.95866</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>7208</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-12.17325</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-76.95738</v>
-      </c>
-      <c r="I54" t="n">
-        <v>343</v>
-      </c>
-      <c r="J54" t="n">
-        <v>19</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-12.17325</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-76.95738</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>7209</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-12.19083</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-76.96129999999999</v>
-      </c>
-      <c r="I55" t="n">
-        <v>376</v>
-      </c>
-      <c r="J55" t="n">
-        <v>17</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-12.19083</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-76.9613</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>JULIO CESAR ESCOBAR</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-12.16274</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-76.9744</v>
-      </c>
-      <c r="I56" t="n">
-        <v>756</v>
-      </c>
-      <c r="J56" t="n">
-        <v>44</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-12.16274</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-76.9744</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-12.1485</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-76.97524</v>
-      </c>
-      <c r="I57" t="n">
-        <v>612</v>
-      </c>
-      <c r="J57" t="n">
-        <v>47</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-12.1485</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-76.97524</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>INGENIERIA DEL SUR</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-12.15576</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-76.97467</v>
-      </c>
-      <c r="I58" t="n">
-        <v>202</v>
-      </c>
-      <c r="J58" t="n">
-        <v>21</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-12.15576</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-76.97467</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>FERMIN TANGUIS</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-12.1553</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-76.97698</v>
-      </c>
-      <c r="I59" t="n">
-        <v>864</v>
-      </c>
-      <c r="J59" t="n">
-        <v>75</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-12.1553</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-76.97698</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>ISAAC NEWTON</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-12.18218</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-76.97882</v>
-      </c>
-      <c r="I60" t="n">
-        <v>339</v>
-      </c>
-      <c r="J60" t="n">
-        <v>21</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-12.18218</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-76.97882</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>MARY'S CHILDREN SCHOOL</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-12.16094</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-76.96305</v>
-      </c>
-      <c r="I61" t="n">
-        <v>179</v>
-      </c>
-      <c r="J61" t="n">
-        <v>6</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-12.16094</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-76.96305</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>MI PEQUEÑO JARDIN</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-12.15766</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-76.96829</v>
-      </c>
-      <c r="I62" t="n">
-        <v>54</v>
-      </c>
-      <c r="J62" t="n">
-        <v>4</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-12.15766</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-76.96829</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>NUESTRA SEÑORA DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-12.1845</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-76.95979</v>
-      </c>
-      <c r="I63" t="n">
-        <v>368</v>
-      </c>
-      <c r="J63" t="n">
-        <v>17</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-12.1845</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-76.95979</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>PITAGORAS</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-12.18782</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-76.97432000000001</v>
-      </c>
-      <c r="I64" t="n">
-        <v>250</v>
-      </c>
-      <c r="J64" t="n">
-        <v>3</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-12.18782</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-76.97432</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>ROSA DE SANTA MARIA</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-12.16351</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-76.97354</v>
-      </c>
-      <c r="I65" t="n">
-        <v>461</v>
-      </c>
-      <c r="J65" t="n">
-        <v>43</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-12.16351</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-76.97354</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>REVERENDO HERMANO GASTON MARIA</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-12.1576</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-76.96416000000001</v>
-      </c>
-      <c r="I66" t="n">
-        <v>578</v>
-      </c>
-      <c r="J66" t="n">
-        <v>34</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-12.1576</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-76.96416</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>SAN BARTOLOME</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-12.17285</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-76.96186</v>
-      </c>
-      <c r="I67" t="n">
-        <v>497</v>
-      </c>
-      <c r="J67" t="n">
-        <v>29</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-12.17285</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-76.96186</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>SANTA RITA DE PAMPLONA</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-12.14428</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-76.96428</v>
-      </c>
-      <c r="I68" t="n">
-        <v>332</v>
-      </c>
-      <c r="J68" t="n">
-        <v>15</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-12.14428</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-76.96428</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>SEÑOR DE ANIMAS</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-12.17415</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-76.96599999999999</v>
-      </c>
-      <c r="I69" t="n">
-        <v>273</v>
-      </c>
-      <c r="J69" t="n">
-        <v>17</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-12.17415</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-76.966</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>INGENIERIA SAN JUAN</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-12.14566</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-76.97098</v>
-      </c>
-      <c r="I70" t="n">
-        <v>364</v>
-      </c>
-      <c r="J70" t="n">
-        <v>14</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-12.14566</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-76.97098</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>ALBERT EINSTEIN</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-12.15593</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-76.96581999999999</v>
-      </c>
-      <c r="I71" t="n">
-        <v>156</v>
-      </c>
-      <c r="J71" t="n">
-        <v>15</v>
-      </c>
-      <c r="K71" t="n">
-        <v>1</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-12.15593</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-76.96582</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>ANDRES BELLO</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-12.16794</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-76.96825</v>
-      </c>
-      <c r="I72" t="n">
-        <v>267</v>
-      </c>
-      <c r="J72" t="n">
-        <v>22</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-12.16794</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-76.96825</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>L'HERMITAGE</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-12.15682</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-76.96774000000001</v>
-      </c>
-      <c r="I73" t="n">
-        <v>236</v>
-      </c>
-      <c r="J73" t="n">
-        <v>23</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-12.15682</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-76.96774</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-12.16347</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-76.96487999999999</v>
-      </c>
-      <c r="I74" t="n">
-        <v>211</v>
-      </c>
-      <c r="J74" t="n">
-        <v>11</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-12.16347</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-76.96488</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>SANTIAGO APOSTOL</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-12.18589</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-76.9629</v>
-      </c>
-      <c r="I75" t="n">
-        <v>333</v>
-      </c>
-      <c r="J75" t="n">
-        <v>18</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-12.18589</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-76.9629</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>SACO OLIVEROS</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-12.16039</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-76.97578</v>
-      </c>
-      <c r="I76" t="n">
-        <v>1066</v>
-      </c>
-      <c r="J76" t="n">
-        <v>28</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-12.16039</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-76.97578</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-12.15076</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-76.9701</v>
-      </c>
-      <c r="I77" t="n">
-        <v>901</v>
-      </c>
-      <c r="J77" t="n">
-        <v>41</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-12.15076</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-76.9701</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>AMERICA SIGLO XXI</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-12.18635</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-76.97633</v>
-      </c>
-      <c r="I78" t="n">
-        <v>517</v>
-      </c>
-      <c r="J78" t="n">
-        <v>30</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-12.18635</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-76.97633</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>LA VILLA DE SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-12.14865</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-76.9683</v>
-      </c>
-      <c r="I79" t="n">
-        <v>211</v>
-      </c>
-      <c r="J79" t="n">
-        <v>14</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-12.14865</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-76.9683</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>HEROES DEL PACIFICO</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-12.17175</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-76.96933</v>
-      </c>
-      <c r="I80" t="n">
-        <v>370</v>
-      </c>
-      <c r="J80" t="n">
-        <v>24</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-12.17175</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-76.96933</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>SAN MARTINCITO DE PORRES</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-12.13873</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-76.9641</v>
-      </c>
-      <c r="I81" t="n">
-        <v>521</v>
-      </c>
-      <c r="J81" t="n">
-        <v>36</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-12.13873</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-76.9641</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>FE Y ALEGRIA 3</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-12.14995</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-76.96923</v>
-      </c>
-      <c r="I82" t="n">
-        <v>1456</v>
-      </c>
-      <c r="J82" t="n">
-        <v>76</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-12.14995</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-76.96923</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1456</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>LUZ Y ESPERANZA</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-12.1714</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-76.97004</v>
-      </c>
-      <c r="I83" t="n">
-        <v>454</v>
-      </c>
-      <c r="J83" t="n">
-        <v>32</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-12.1714</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-76.97004</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4785,20 +5593,30 @@
           <t>SEÑOR DE LA JUSTICIA</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-12.18562</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-76.95493</v>
-      </c>
-      <c r="I84" t="n">
-        <v>241</v>
-      </c>
-      <c r="J84" t="n">
-        <v>16</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-12.18562</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-76.95493</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4837,20 +5655,30 @@
           <t>SANTA MARIA</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>-12.16516</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-76.95726999999999</v>
-      </c>
-      <c r="I85" t="n">
-        <v>251</v>
-      </c>
-      <c r="J85" t="n">
-        <v>19</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-12.16516</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-76.95727</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4889,20 +5717,30 @@
           <t>JEAN PIAGET</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>-12.16092</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-76.97411</v>
-      </c>
-      <c r="I86" t="n">
-        <v>240</v>
-      </c>
-      <c r="J86" t="n">
-        <v>10</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-12.16092</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-76.97411</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4941,20 +5779,30 @@
           <t>LEONARD EULER</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>-12.16805</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-76.97689</v>
-      </c>
-      <c r="I87" t="n">
-        <v>222</v>
-      </c>
-      <c r="J87" t="n">
-        <v>12</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-12.16805</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-76.97689</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4993,20 +5841,30 @@
           <t>NIÑO JESUS DIVINO</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>-12.16779</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-76.98284</v>
-      </c>
-      <c r="I88" t="n">
-        <v>225</v>
-      </c>
-      <c r="J88" t="n">
-        <v>14</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-12.16779</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-76.98284</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5045,20 +5903,30 @@
           <t>FE Y ALEGRIA 65</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>-12.12732</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-76.94741</v>
-      </c>
-      <c r="I89" t="n">
-        <v>693</v>
-      </c>
-      <c r="J89" t="n">
-        <v>38</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-12.12732</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-76.94741</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5097,20 +5965,30 @@
           <t>TALENTOS KIDS</t>
         </is>
       </c>
-      <c r="G90" t="n">
-        <v>-12.17971</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-76.98159</v>
-      </c>
-      <c r="I90" t="n">
-        <v>193</v>
-      </c>
-      <c r="J90" t="n">
-        <v>11</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-12.17971</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-76.98159</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5149,20 +6027,30 @@
           <t>JOHANNES GUTENBERG SCHOOL</t>
         </is>
       </c>
-      <c r="G91" t="n">
-        <v>-12.15482</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-76.96414</v>
-      </c>
-      <c r="I91" t="n">
-        <v>318</v>
-      </c>
-      <c r="J91" t="n">
-        <v>20</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-12.15482</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-76.96414</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5201,20 +6089,30 @@
           <t>JESUS OBRERO</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>-12.13161</v>
-      </c>
-      <c r="H92" t="n">
-        <v>-76.96125000000001</v>
-      </c>
-      <c r="I92" t="n">
-        <v>299</v>
-      </c>
-      <c r="J92" t="n">
-        <v>14</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-12.13161</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-76.96125</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -5253,20 +6151,30 @@
           <t>AMERICAN CHILDREN HIGH SCHOOL</t>
         </is>
       </c>
-      <c r="G93" t="n">
-        <v>-12.18525</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-76.98003</v>
-      </c>
-      <c r="I93" t="n">
-        <v>285</v>
-      </c>
-      <c r="J93" t="n">
-        <v>18</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-12.18525</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-76.98003</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5305,20 +6213,30 @@
           <t>EMMANUEL COLLEGE</t>
         </is>
       </c>
-      <c r="G94" t="n">
-        <v>-12.16215</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-76.96257</v>
-      </c>
-      <c r="I94" t="n">
-        <v>61</v>
-      </c>
-      <c r="J94" t="n">
-        <v>7</v>
-      </c>
-      <c r="K94" t="n">
-        <v>1</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-12.16215</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-76.96257</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -5357,20 +6275,30 @@
           <t>EMMANUEL COLLEGE</t>
         </is>
       </c>
-      <c r="G95" t="n">
-        <v>-12.16197</v>
-      </c>
-      <c r="H95" t="n">
-        <v>-76.96249</v>
-      </c>
-      <c r="I95" t="n">
-        <v>62</v>
-      </c>
-      <c r="J95" t="n">
-        <v>5</v>
-      </c>
-      <c r="K95" t="n">
-        <v>1</v>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-12.16197</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-76.96249</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5409,20 +6337,30 @@
           <t>SOR MARIA DE LOS ANGELES</t>
         </is>
       </c>
-      <c r="G96" t="n">
-        <v>-12.13735</v>
-      </c>
-      <c r="H96" t="n">
-        <v>-76.96742</v>
-      </c>
-      <c r="I96" t="n">
-        <v>255</v>
-      </c>
-      <c r="J96" t="n">
-        <v>13</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-12.13735</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-76.96742</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5461,20 +6399,30 @@
           <t>LATINO</t>
         </is>
       </c>
-      <c r="G97" t="n">
-        <v>-12.15994</v>
-      </c>
-      <c r="H97" t="n">
-        <v>-76.98174</v>
-      </c>
-      <c r="I97" t="n">
-        <v>324</v>
-      </c>
-      <c r="J97" t="n">
-        <v>24</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-12.15994</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-76.98174</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5513,20 +6461,30 @@
           <t>JESUS OBRERO DE OLLANTAY</t>
         </is>
       </c>
-      <c r="G98" t="n">
-        <v>-12.13217</v>
-      </c>
-      <c r="H98" t="n">
-        <v>-76.96347</v>
-      </c>
-      <c r="I98" t="n">
-        <v>548</v>
-      </c>
-      <c r="J98" t="n">
-        <v>32</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-12.13217</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-76.96347</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5565,20 +6523,30 @@
           <t>ANNIE'S SCHOOL</t>
         </is>
       </c>
-      <c r="G99" t="n">
-        <v>-12.16241</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-76.96204</v>
-      </c>
-      <c r="I99" t="n">
-        <v>1107</v>
-      </c>
-      <c r="J99" t="n">
-        <v>40</v>
-      </c>
-      <c r="K99" t="n">
-        <v>1</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-12.16241</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-76.96204</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5617,20 +6585,30 @@
           <t>SOR MARIA DE LOS ANGELES II</t>
         </is>
       </c>
-      <c r="G100" t="n">
-        <v>-12.136996</v>
-      </c>
-      <c r="H100" t="n">
-        <v>-76.967061</v>
-      </c>
-      <c r="I100" t="n">
-        <v>201</v>
-      </c>
-      <c r="J100" t="n">
-        <v>13</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-12.136996</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-76.967061</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-LIMA-SAN_JUAN_DE_MIRAFLORES.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SAN_JUAN_DE_MIRAFLORES.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>59104</t>
+          <t>329243</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LEONARD EULER II</t>
+          <t>537 LOS LAURELES</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.16352</t>
+          <t>-12.14733</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.97335</t>
+          <t>-76.96239</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>221</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>326763</t>
+          <t>332127</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CRISTO SEMBRADOR</t>
+          <t>JEAN PIAGET</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.13875</t>
+          <t>-12.16092</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.96307</t>
+          <t>-76.97411</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>329182</t>
+          <t>329709</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>46 MI JARDIN DE AMOR</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.15124</t>
+          <t>-12.13536</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.97361</t>
+          <t>-76.95962</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>329196</t>
+          <t>329399</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>56 MI DULCE HOGAR</t>
+          <t>635 EL UNIVERSO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.15342</t>
+          <t>-12.18626</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.96783</t>
+          <t>-76.95811</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>329200</t>
+          <t>329484</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>66 NIÑO JESUS DE PRAGA</t>
+          <t>7223 MIGUEL COLINA MARIE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.14809</t>
+          <t>-12.15372</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.97192</t>
+          <t>-76.9797</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>290</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>329219</t>
+          <t>329592</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>513 NIÑOS DE MARIA</t>
+          <t>6037 INCA PACHACUTEC</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.16988</t>
+          <t>-12.15624</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.97503</t>
+          <t>-76.96192</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>329224</t>
+          <t>331038</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>514 EL CARMEN</t>
+          <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.16368</t>
+          <t>-12.16347</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.97778</t>
+          <t>-76.96488</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>329238</t>
+          <t>614443</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>530 VIRGEN DE FATIMA</t>
+          <t>TALENTOS KIDS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.15953</t>
+          <t>-12.17971</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.96722</t>
+          <t>-76.98159</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>193</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>329243</t>
+          <t>329281</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>537 LOS LAURELES</t>
+          <t>551</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.14733</t>
+          <t>-12.13602</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.96239</t>
+          <t>-76.96065</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>269</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>329257</t>
+          <t>329380</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JESUS NIÑO</t>
+          <t>7219 ARISTOTELES</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.16629</t>
+          <t>-12.18595</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.97278</t>
+          <t>-76.95748</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>245</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>329262</t>
+          <t>329422</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>541 DIVINO NIÑO JESUS</t>
+          <t>638 PAMPAS DE SAN JUAN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.13875</t>
+          <t>-12.1668</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.97184</t>
+          <t>-76.96566</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>245</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>329276</t>
+          <t>329587</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>547 JESUS PODEROSO</t>
+          <t>652 27 LA MERCED DE LIMA / 7229 LA MERCED DE LIMA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.14829</t>
+          <t>-12.18287</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.98153</t>
+          <t>-76.95871</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>276</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,27 +1245,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>329281</t>
+          <t>332132</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>LEONARD EULER</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.13602</t>
+          <t>-12.16805</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.96065</t>
+          <t>-76.97689</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>329295</t>
+          <t>329196</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>559 SAGRADO CORAZON DE JESUS</t>
+          <t>56 MI DULCE HOGAR</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.17768</t>
+          <t>-12.15342</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.97801</t>
+          <t>-76.96783</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>329304</t>
+          <t>329219</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>623 / 7101</t>
+          <t>513 NIÑOS DE MARIA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.18447</t>
+          <t>-12.16988</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.97897</t>
+          <t>-76.97503</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>268</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>329337</t>
+          <t>688820</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>627 / 7212</t>
+          <t>SOR MARIA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.17348</t>
+          <t>-12.13735</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.96406</t>
+          <t>-76.96742</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>255</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>329342</t>
+          <t>902009</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>629-6034 CESAR CARBONEL RODRIGUEZ</t>
+          <t>SOR MARIA DE LOS ANGELES II</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.14525</t>
+          <t>-12.136996</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.9757</t>
+          <t>-76.967061</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>329356</t>
+          <t>329182</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>630 JUAN PABLO II</t>
+          <t>46 MI JARDIN DE AMOR</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.1394</t>
+          <t>-12.15124</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.95698</t>
+          <t>-76.97361</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>325</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>329380</t>
+          <t>330755</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7219 ARISTOTELES</t>
+          <t>INGENIERIA SAN JUAN</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.18595</t>
+          <t>-12.14566</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.95748</t>
+          <t>-76.97098</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>364</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>329399</t>
+          <t>331566</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>635 EL UNIVERSO</t>
+          <t>LA VILLA DE SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.18626</t>
+          <t>-12.14865</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.95811</t>
+          <t>-76.9683</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>329417</t>
+          <t>342112</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>637 VALLE SHARON</t>
+          <t>NIÑO JESUS DIVINO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.17238</t>
+          <t>-12.16779</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.97072</t>
+          <t>-76.98284</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>225</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>329422</t>
+          <t>686519</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>638 PAMPAS DE SAN JUAN</t>
+          <t>JESUS OBRERO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.1668</t>
+          <t>-12.13161</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.96566</t>
+          <t>-76.96125</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>299</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>329484</t>
+          <t>329262</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7223 MIGUEL COLINA MARIE</t>
+          <t>541 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.15372</t>
+          <t>-12.13875</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.9797</t>
+          <t>-76.97184</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>343</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>329498</t>
+          <t>330699</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>652 12 VIRGEN DEL BUEN PASO</t>
+          <t>SANTA RITA DE PAMPLONA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.14156</t>
+          <t>-12.14428</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.9625</t>
+          <t>-76.96428</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>332</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,42 +1989,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>329506</t>
+          <t>330901</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>652 13 LOS TREBOLITOS</t>
+          <t>ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.17753</t>
+          <t>-12.15593</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.96367</t>
+          <t>-76.96582</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>156</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>329549</t>
+          <t>326763</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>652 19 HORACIO ZEBALLOS GAMEZ / 7227 HORACIO ZEBALLOS GAMEZ</t>
+          <t>CRISTO SEMBRADOR</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.1408</t>
+          <t>-12.13875</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.97873</t>
+          <t>-76.96307</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>314</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>329587</t>
+          <t>329200</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>652 27 LA MERCED DE LIMA / 7229 LA MERCED DE LIMA</t>
+          <t>66 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.18287</t>
+          <t>-12.14809</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.95871</t>
+          <t>-76.97192</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>368</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>329592</t>
+          <t>329356</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>6037 INCA PACHACUTEC</t>
+          <t>630 JUAN PABLO II</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.15624</t>
+          <t>-12.1394</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.96192</t>
+          <t>-76.95698</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>329610</t>
+          <t>329498</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6037 INCA PACHACUTEC</t>
+          <t>652 12 VIRGEN DEL BUEN PASO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.15682</t>
+          <t>-12.14156</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.964</t>
+          <t>-76.9625</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>335</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>329634</t>
+          <t>331929</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>SEÑOR DE LA JUSTICIA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.1444</t>
+          <t>-12.18562</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.97127</t>
+          <t>-76.95493</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>241</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>329648</t>
+          <t>329224</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>6045 DOLORES CAVERO DE GRAU</t>
+          <t>514 EL CARMEN</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.15338</t>
+          <t>-12.16368</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.96729</t>
+          <t>-76.97778</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>421</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>329653</t>
+          <t>329257</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>JESUS NIÑO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.14849</t>
+          <t>-12.16629</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.97236</t>
+          <t>-76.97278</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>453</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>329667</t>
+          <t>329907</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.15807</t>
+          <t>-12.19083</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.96832</t>
+          <t>-76.9613</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>376</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>329672</t>
+          <t>330454</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>6089 JORGE BASADRE GROHMANN</t>
+          <t>NUESTRA SEÑORA DE GUADALUPE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.14668</t>
+          <t>-12.1845</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.96287</t>
+          <t>-76.95979</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>368</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>329686</t>
+          <t>330722</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>6096 ANTONIO RAIMONDI</t>
+          <t>SEÑOR DE ANIMAS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.16712</t>
+          <t>-12.17415</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.96474</t>
+          <t>-76.966</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>273</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>329691</t>
+          <t>329276</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>6151 SAN LUIS GONZAGA</t>
+          <t>547 JESUS PODEROSO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.13945</t>
+          <t>-12.14829</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.97141</t>
+          <t>-76.98153</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>344</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>329709</t>
+          <t>331156</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>SANTIAGO APOSTOL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.13536</t>
+          <t>-12.18589</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.95962</t>
+          <t>-76.9629</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>333</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>329714</t>
+          <t>688212</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>7041 VIRGEN DE LA MERCED</t>
+          <t>AMERICAN CHILDREN HIGH SCHOOL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.16793</t>
+          <t>-12.18525</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.95869</t>
+          <t>-76.98003</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>329728</t>
+          <t>329894</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>7059 JOSE ANTONIO ENCINAS FRANCO</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.14751</t>
+          <t>-12.17325</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.96546</t>
+          <t>-76.95738</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>343</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>329733</t>
+          <t>332108</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>7060 ANDRES AVELINO CACERES</t>
+          <t>SANTA MARIA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.15274</t>
+          <t>-12.16516</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.96267</t>
+          <t>-76.95727</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>251</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>329747</t>
+          <t>329337</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>7061 LOS HEROES DE SAN JUAN</t>
+          <t>627 / 7212</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.15593</t>
+          <t>-12.17348</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.97544</t>
+          <t>-76.96406</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>468</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>329752</t>
+          <t>329417</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>7062 NACIONES UNIDAS</t>
+          <t>637 VALLE SHARON</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.15619</t>
+          <t>-12.17238</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.97483</t>
+          <t>-76.97072</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>447</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>329766</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>7063 ANDRES AVELINO CACERES</t>
+          <t>JOHANNES GUTENBERG SCHOOL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.16747</t>
+          <t>-12.15482</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.97415</t>
+          <t>-76.96414</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>318</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>329771</t>
+          <t>329238</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>7067 TORIBIO SEMINARIO</t>
+          <t>530 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.15079</t>
+          <t>-12.15953</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-76.97775</t>
+          <t>-76.96722</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>514</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>329785</t>
+          <t>330114</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>7069 CESAR VALLEJO</t>
+          <t>INGENIERIA DEL SUR</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.15099</t>
+          <t>-12.15576</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-76.97448</t>
+          <t>-76.97467</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>202</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>329790</t>
+          <t>330208</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>7070 DRA. MARIA REICHE GROSSE NEUMAN</t>
+          <t>ISAAC NEWTON</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.16776</t>
+          <t>-12.18218</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-76.97258</t>
+          <t>-76.97882</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>339</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>329808</t>
+          <t>330920</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>7074 LA INMACULADA</t>
+          <t>ANDRES BELLO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.137</t>
+          <t>-12.16794</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-76.96824</t>
+          <t>-76.96825</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>267</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>329813</t>
+          <t>59104</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>7081 JOSE MARIA ARGUEDAS A</t>
+          <t>LEONARD EULER II</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.17933</t>
+          <t>-12.16352</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-76.97971</t>
+          <t>-76.97335</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>418</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>329832</t>
+          <t>329549</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>7082 JUAN DE ESPINOSA MEDRANO</t>
+          <t>652 19 HORACIO ZEBALLOS GAMEZ / 7227 HORACIO ZEBALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.13264</t>
+          <t>-12.1408</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-76.96277</t>
+          <t>-76.97873</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>442</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>329846</t>
+          <t>329733</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>7087 EL NAZARENO</t>
+          <t>7060 ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.13769</t>
+          <t>-12.15274</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-76.95633</t>
+          <t>-76.96267</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>432</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>329851</t>
+          <t>330996</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>7099 HECTOR PRETELL / 7099 HECTOR PRETELL CARBONELL</t>
+          <t>L'HERMITAGE</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.17726</t>
+          <t>-12.15682</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-76.96907</t>
+          <t>-76.96774</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>236</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>329865</t>
+          <t>331694</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>7100 REPUBLICA ALEMANA</t>
+          <t>HEROES DEL PACIFICO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.18017</t>
+          <t>-12.17175</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-76.95866</t>
+          <t>-76.96933</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>370</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>329894</t>
+          <t>688844</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>7208</t>
+          <t>LATINO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-12.17325</t>
+          <t>-12.15994</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-76.95738</t>
+          <t>-76.98174</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>324</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>329907</t>
+          <t>329714</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>7041 VIRGEN DE LA MERCED</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-12.19083</t>
+          <t>-12.16793</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-76.9613</t>
+          <t>-76.95869</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>746</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>329969</t>
+          <t>329766</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>JULIO CESAR ESCOBAR</t>
+          <t>7063 ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-12.16274</t>
+          <t>-12.16747</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-76.9744</t>
+          <t>-76.97415</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>668</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>329993</t>
+          <t>331199</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-12.1485</t>
+          <t>-12.16039</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-76.97524</t>
+          <t>-76.97578</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>330114</t>
+          <t>329667</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>INGENIERIA DEL SUR</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-12.15576</t>
+          <t>-12.15807</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-76.97467</t>
+          <t>-76.96832</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>733</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>330171</t>
+          <t>330562</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FERMIN TANGUIS</t>
+          <t>SAN BARTOLOME</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-12.1553</t>
+          <t>-12.17285</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-76.97698</t>
+          <t>-76.96186</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>497</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>330208</t>
+          <t>330500</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ISAAC NEWTON</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-12.18218</t>
+          <t>-12.18782</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-76.97882</t>
+          <t>-76.97432</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>330350</t>
+          <t>329851</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MARY'S CHILDREN SCHOOL</t>
+          <t>7099 HECTOR PRETELL / 7099 HECTOR PRETELL CARBONELL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-12.16094</t>
+          <t>-12.17726</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-76.96305</t>
+          <t>-76.96907</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>646</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>330393</t>
+          <t>331439</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MI PEQUEÑO JARDIN</t>
+          <t>AMERICA SIGLO XXI</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-12.15766</t>
+          <t>-12.18635</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-76.96829</t>
+          <t>-76.97633</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>517</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>330454</t>
+          <t>331910</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE GUADALUPE</t>
+          <t>LUZ Y ESPERANZA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-12.1845</t>
+          <t>-12.1714</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-76.95979</t>
+          <t>-76.97004</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>454</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>330500</t>
+          <t>735807</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>JESUS OBRERO DE OLLANTAY</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-12.18782</t>
+          <t>-12.13217</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-76.97432</t>
+          <t>-76.96347</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>548</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>330519</t>
+          <t>329342</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ROSA DE SANTA MARIA</t>
+          <t>629-6034 CESAR CARBONEL RODRIGUEZ</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-12.16351</t>
+          <t>-12.14525</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-76.97354</t>
+          <t>-76.9757</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>674</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>330562</t>
+          <t>331731</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SAN BARTOLOME</t>
+          <t>SAN MARTINCITO DE PORRES</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-12.17285</t>
+          <t>-12.13873</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-76.96186</t>
+          <t>-76.9641</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>521</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>330699</t>
+          <t>329686</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SANTA RITA DE PAMPLONA</t>
+          <t>6096 ANTONIO RAIMONDI</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-12.14428</t>
+          <t>-12.16712</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-76.96428</t>
+          <t>-76.96474</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>797</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>330722</t>
+          <t>329771</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SEÑOR DE ANIMAS</t>
+          <t>7067 TORIBIO SEMINARIO</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-12.17415</t>
+          <t>-12.15079</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-76.966</t>
+          <t>-76.97775</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>606</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>330755</t>
+          <t>495746</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>INGENIERIA SAN JUAN</t>
+          <t>FE Y ALEGRIA 65</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-12.14566</t>
+          <t>-12.12732</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-76.97098</t>
+          <t>-76.94741</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>693</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,37 +4779,37 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>330901</t>
+          <t>329832</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ALBERT EINSTEIN</t>
+          <t>7082 JUAN DE ESPINOSA MEDRANO</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-12.15593</t>
+          <t>-12.13264</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-76.96582</t>
+          <t>-76.96277</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>784</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>330920</t>
+          <t>330393</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ANDRES BELLO</t>
+          <t>MI PEQUEÑO JARDIN</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-12.16794</t>
+          <t>-12.15766</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-76.96825</t>
+          <t>-76.96829</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>330996</t>
+          <t>329653</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>L'HERMITAGE</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-12.15682</t>
+          <t>-12.14849</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-76.96774</t>
+          <t>-76.97236</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>873</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,37 +4965,37 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>331038</t>
+          <t>787009</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL CARMEN</t>
+          <t>ANNIE'S SCHOOL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-12.16347</t>
+          <t>-12.16241</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-76.96488</t>
+          <t>-76.96204</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>331156</t>
+          <t>331335</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SANTIAGO APOSTOL</t>
+          <t>NIÑO JESUS</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-12.18589</t>
+          <t>-12.15076</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-76.9629</t>
+          <t>-76.9701</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>901</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>331199</t>
+          <t>330519</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS</t>
+          <t>ROSA DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-12.16039</t>
+          <t>-12.16351</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-76.97578</t>
+          <t>-76.97354</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>461</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>331335</t>
+          <t>329969</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>NIÑO JESUS</t>
+          <t>JULIO CESAR ESCOBAR</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-12.15076</t>
+          <t>-12.16274</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-76.9701</t>
+          <t>-76.9744</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>756</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>331439</t>
+          <t>329865</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>AMERICA SIGLO XXI</t>
+          <t>7100 REPUBLICA ALEMANA</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-12.18635</t>
+          <t>-12.18017</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-76.97633</t>
+          <t>-76.95866</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>792</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>331566</t>
+          <t>329634</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>LA VILLA DE SAN FRANCISCO DE ASIS</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-12.14865</t>
+          <t>-12.1444</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-76.9683</t>
+          <t>-76.97127</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>949</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>331694</t>
+          <t>329808</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>HEROES DEL PACIFICO</t>
+          <t>7074 LA INMACULADA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-12.17175</t>
+          <t>-12.137</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-76.96933</t>
+          <t>-76.96824</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>331731</t>
+          <t>329993</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SAN MARTINCITO DE PORRES</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-12.13873</t>
+          <t>-12.1485</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-76.9641</t>
+          <t>-76.97524</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>612</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,37 +5461,37 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>331745</t>
+          <t>688580</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 3</t>
+          <t>EMMANUEL COLLEGE</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-12.14995</t>
+          <t>-12.16197</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-76.96923</t>
+          <t>-76.96249</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>62</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>331910</t>
+          <t>329648</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>LUZ Y ESPERANZA</t>
+          <t>6045 DOLORES CAVERO DE GRAU</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-12.1714</t>
+          <t>-12.15338</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-76.97004</t>
+          <t>-76.96729</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>827</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>331929</t>
+          <t>329846</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SEÑOR DE LA JUSTICIA</t>
+          <t>7087 EL NAZARENO</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-12.18562</t>
+          <t>-12.13769</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-76.95493</t>
+          <t>-76.95633</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>896</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>332108</t>
+          <t>329790</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>SANTA MARIA</t>
+          <t>7070 DRA. MARIA REICHE GROSSE NEUMAN</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-12.16516</t>
+          <t>-12.16776</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-76.95727</t>
+          <t>-76.97258</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>332127</t>
+          <t>329304</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>JEAN PIAGET</t>
+          <t>623 / 7101</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-12.16092</t>
+          <t>-12.18447</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-76.97411</t>
+          <t>-76.97897</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>332132</t>
+          <t>329610</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>LEONARD EULER</t>
+          <t>6037 INCA PACHACUTEC</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-12.16805</t>
+          <t>-12.15682</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-76.97689</t>
+          <t>-76.964</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>342112</t>
+          <t>329672</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NIÑO JESUS DIVINO</t>
+          <t>6089 JORGE BASADRE GROHMANN</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-12.16779</t>
+          <t>-12.14668</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-76.98284</t>
+          <t>-76.96287</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>495746</t>
+          <t>329728</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 65</t>
+          <t>7059 JOSE ANTONIO ENCINAS FRANCO</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-12.12732</t>
+          <t>-12.14751</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-76.94741</t>
+          <t>-76.96546</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>614443</t>
+          <t>329747</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>TALENTOS KIDS</t>
+          <t>7061 LOS HEROES DE SAN JUAN</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-12.17971</t>
+          <t>-12.15593</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-76.98159</t>
+          <t>-76.97544</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>625700</t>
+          <t>330350</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>JOHANNES GUTENBERG SCHOOL</t>
+          <t>MARY'S CHILDREN SCHOOL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-12.15482</t>
+          <t>-12.16094</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-76.96414</t>
+          <t>-76.96305</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>179</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6081,32 +6081,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>686519</t>
+          <t>329813</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>JESUS OBRERO</t>
+          <t>7081 JOSE MARIA ARGUEDAS A</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-12.13161</t>
+          <t>-12.17933</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-76.96125</t>
+          <t>-76.97971</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6143,32 +6143,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>688212</t>
+          <t>329691</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AMERICAN CHILDREN HIGH SCHOOL</t>
+          <t>6151 SAN LUIS GONZAGA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-12.18525</t>
+          <t>-12.13945</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-76.98003</t>
+          <t>-76.97141</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6267,42 +6267,42 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>688580</t>
+          <t>329785</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>EMMANUEL COLLEGE</t>
+          <t>7069 CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-12.16197</t>
+          <t>-12.15099</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-76.96249</t>
+          <t>-76.97448</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6329,32 +6329,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>688820</t>
+          <t>330171</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SOR MARIA DE LOS ANGELES</t>
+          <t>FERMIN TANGUIS</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-12.13735</t>
+          <t>-12.1553</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-76.96742</t>
+          <t>-76.97698</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>864</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>688844</t>
+          <t>331745</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>LATINO</t>
+          <t>FE Y ALEGRIA 3</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-12.15994</t>
+          <t>-12.14995</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-76.98174</t>
+          <t>-76.96923</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>76</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>735807</t>
+          <t>329752</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>JESUS OBRERO DE OLLANTAY</t>
+          <t>7062 NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-12.13217</t>
+          <t>-12.15619</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-76.96347</t>
+          <t>-76.97483</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6515,42 +6515,42 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>787009</t>
+          <t>329295</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ANNIE'S SCHOOL</t>
+          <t>559 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-12.16241</t>
+          <t>-12.17768</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-76.96204</t>
+          <t>-76.97801</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6577,32 +6577,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>902009</t>
+          <t>329506</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SOR MARIA DE LOS ANGELES II</t>
+          <t>652 13 LOS TREBOLITOS</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-12.136996</t>
+          <t>-12.17753</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-76.967061</t>
+          <t>-76.96367</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>193</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-SAN_JUAN_DE_MIRAFLORES.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SAN_JUAN_DE_MIRAFLORES.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>329243</t>
+          <t>902009</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>537 LOS LAURELES</t>
+          <t>SOR MARIA DE LOS ANGELES II</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.14733</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.96239</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>-12.136996</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.967061</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>332127</t>
+          <t>787009</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JEAN PIAGET</t>
+          <t>ANNIE'S SCHOOL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.16092</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.97411</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>-12.16241</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.96204</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>329709</t>
+          <t>735807</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>JESUS OBRERO DE OLLANTAY</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.13536</t>
+          <t>548</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.95962</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>-12.13217</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>-76.96347</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>329399</t>
+          <t>688844</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>635 EL UNIVERSO</t>
+          <t>LATINO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.18626</t>
+          <t>324</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.95811</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-12.15994</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.98174</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>329484</t>
+          <t>688820</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>7223 MIGUEL COLINA MARIE</t>
+          <t>SOR MARIA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.15372</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.9797</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>-12.13735</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.96742</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>329592</t>
+          <t>688580</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>6037 INCA PACHACUTEC</t>
+          <t>EMMANUEL COLLEGE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.15624</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.96192</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-12.16197</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.96249</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>331038</t>
+          <t>688575</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL CARMEN</t>
+          <t>EMMANUEL COLLEGE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.16347</t>
+          <t>61</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.96488</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>-12.16215</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.96257</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>614443</t>
+          <t>688212</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TALENTOS KIDS</t>
+          <t>AMERICAN CHILDREN HIGH SCHOOL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.17971</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.98159</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>-12.18525</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.98003</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>329281</t>
+          <t>686519</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>JESUS OBRERO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.13602</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.96065</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>-12.13161</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.96125</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>329380</t>
+          <t>625700</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7219 ARISTOTELES</t>
+          <t>JOHANNES GUTENBERG SCHOOL</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.18595</t>
+          <t>318</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.95748</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>-12.15482</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.96414</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>329422</t>
+          <t>614443</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>638 PAMPAS DE SAN JUAN</t>
+          <t>TALENTOS KIDS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.1668</t>
+          <t>193</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.96566</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>-12.17971</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.98159</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>329587</t>
+          <t>495746</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>652 27 LA MERCED DE LIMA / 7229 LA MERCED DE LIMA</t>
+          <t>FE Y ALEGRIA 65</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.18287</t>
+          <t>693</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.95871</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>-12.12732</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.94741</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>332132</t>
+          <t>342112</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LEONARD EULER</t>
+          <t>NIÑO JESUS DIVINO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.16805</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.97689</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>-12.16779</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.98284</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>329196</t>
+          <t>332132</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>56 MI DULCE HOGAR</t>
+          <t>LEONARD EULER</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.15342</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.96783</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>-12.16805</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.97689</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>329219</t>
+          <t>332127</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>513 NIÑOS DE MARIA</t>
+          <t>JEAN PIAGET</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.16988</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.97503</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>-12.16092</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.97411</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>688820</t>
+          <t>332108</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SOR MARIA DE LOS ANGELES</t>
+          <t>SANTA MARIA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.13735</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.96742</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>-12.16516</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.95727</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>902009</t>
+          <t>331929</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SOR MARIA DE LOS ANGELES II</t>
+          <t>SEÑOR DE LA JUSTICIA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.136996</t>
+          <t>241</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.967061</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>-12.18562</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.95493</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>329182</t>
+          <t>331910</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>46 MI JARDIN DE AMOR</t>
+          <t>LUZ Y ESPERANZA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.15124</t>
+          <t>454</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.97361</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>-12.1714</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.97004</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>330755</t>
+          <t>331745</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>INGENIERIA SAN JUAN</t>
+          <t>FE Y ALEGRIA 3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.14566</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.97098</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>-12.14995</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.96923</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>331566</t>
+          <t>331731</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>LA VILLA DE SAN FRANCISCO DE ASIS</t>
+          <t>SAN MARTINCITO DE PORRES</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.14865</t>
+          <t>521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.9683</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>-12.13873</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.9641</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>342112</t>
+          <t>331694</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NIÑO JESUS DIVINO</t>
+          <t>HEROES DEL PACIFICO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.16779</t>
+          <t>370</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.98284</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>-12.17175</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.96933</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>686519</t>
+          <t>331566</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JESUS OBRERO</t>
+          <t>LA VILLA DE SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.13161</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.96125</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>-12.14865</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.9683</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>329262</t>
+          <t>331439</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>541 DIVINO NIÑO JESUS</t>
+          <t>AMERICA SIGLO XXI</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.13875</t>
+          <t>517</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.97184</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>-12.18635</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.97633</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>330699</t>
+          <t>331335</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SANTA RITA DE PAMPLONA</t>
+          <t>NIÑO JESUS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.14428</t>
+          <t>901</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.96428</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>-12.15076</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.9701</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,37 +1989,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>330901</t>
+          <t>331199</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ALBERT EINSTEIN</t>
+          <t>SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.15593</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.96582</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>-12.16039</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.97578</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>326763</t>
+          <t>331156</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CRISTO SEMBRADOR</t>
+          <t>SANTIAGO APOSTOL</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.13875</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.96307</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>-12.18589</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.9629</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>329200</t>
+          <t>331038</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>66 NIÑO JESUS DE PRAGA</t>
+          <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.14809</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.97192</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>-12.16347</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.96488</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>329356</t>
+          <t>330996</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>630 JUAN PABLO II</t>
+          <t>L'HERMITAGE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.1394</t>
+          <t>236</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.95698</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>-12.15682</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.96774</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>329498</t>
+          <t>330920</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>652 12 VIRGEN DEL BUEN PASO</t>
+          <t>ANDRES BELLO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.14156</t>
+          <t>267</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.9625</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>-12.16794</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.96825</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,37 +2299,37 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>331929</t>
+          <t>330901</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SEÑOR DE LA JUSTICIA</t>
+          <t>ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.18562</t>
+          <t>156</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.95493</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>-12.15593</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.96582</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>329224</t>
+          <t>330755</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>514 EL CARMEN</t>
+          <t>INGENIERIA SAN JUAN</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.16368</t>
+          <t>364</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.97778</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>-12.14566</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.97098</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>329257</t>
+          <t>330722</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>JESUS NIÑO</t>
+          <t>SEÑOR DE ANIMAS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.16629</t>
+          <t>273</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.97278</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>-12.17415</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.966</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>329907</t>
+          <t>330699</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>SANTA RITA DE PAMPLONA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.19083</t>
+          <t>332</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.9613</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>-12.14428</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.96428</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>330454</t>
+          <t>330562</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE GUADALUPE</t>
+          <t>SAN BARTOLOME</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.1845</t>
+          <t>497</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.95979</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>-12.17285</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.96186</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>330722</t>
+          <t>330524</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SEÑOR DE ANIMAS</t>
+          <t>REVERENDO HERMANO GASTON MARIA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.17415</t>
+          <t>578</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.966</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>-12.1576</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.96416</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>329276</t>
+          <t>330519</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>547 JESUS PODEROSO</t>
+          <t>ROSA DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.14829</t>
+          <t>461</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.98153</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>-12.16351</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.97354</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>331156</t>
+          <t>330500</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SANTIAGO APOSTOL</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.18589</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.9629</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>-12.18782</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.97432</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>688212</t>
+          <t>330454</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AMERICAN CHILDREN HIGH SCHOOL</t>
+          <t>NUESTRA SEÑORA DE GUADALUPE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.18525</t>
+          <t>368</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.98003</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>-12.1845</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.95979</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>329894</t>
+          <t>330393</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>7208</t>
+          <t>MI PEQUEÑO JARDIN</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.17325</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.95738</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>-12.15766</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.96829</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>332108</t>
+          <t>330350</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SANTA MARIA</t>
+          <t>MARY'S CHILDREN SCHOOL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.16516</t>
+          <t>179</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.95727</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>-12.16094</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.96305</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>329337</t>
+          <t>330208</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>627 / 7212</t>
+          <t>ISAAC NEWTON</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.17348</t>
+          <t>339</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.96406</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>-12.18218</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.97882</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>329417</t>
+          <t>330171</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>637 VALLE SHARON</t>
+          <t>FERMIN TANGUIS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.17238</t>
+          <t>864</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.97072</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>-12.1553</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.97698</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>625700</t>
+          <t>330114</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>JOHANNES GUTENBERG SCHOOL</t>
+          <t>INGENIERIA DEL SUR</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.15482</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.96414</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>-12.15576</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.97467</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>329238</t>
+          <t>329993</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>530 VIRGEN DE FATIMA</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.15953</t>
+          <t>612</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-76.96722</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>-12.1485</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-76.97524</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>330114</t>
+          <t>329969</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>INGENIERIA DEL SUR</t>
+          <t>JULIO CESAR ESCOBAR</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.15576</t>
+          <t>756</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-76.97467</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>-12.16274</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-76.9744</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>330208</t>
+          <t>329907</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ISAAC NEWTON</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.18218</t>
+          <t>376</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-76.97882</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>-12.19083</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-76.9613</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>330920</t>
+          <t>329894</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ANDRES BELLO</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.16794</t>
+          <t>343</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-76.96825</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>-12.17325</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.95738</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>59104</t>
+          <t>329865</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LEONARD EULER II</t>
+          <t>7100 REPUBLICA ALEMANA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.16352</t>
+          <t>792</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-76.97335</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>-12.18017</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.95866</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>329549</t>
+          <t>329851</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>652 19 HORACIO ZEBALLOS GAMEZ / 7227 HORACIO ZEBALLOS GAMEZ</t>
+          <t>7099 HECTOR PRETELL / 7099 HECTOR PRETELL CARBONELL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.1408</t>
+          <t>646</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-76.97873</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>-12.17726</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.96907</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>329733</t>
+          <t>329846</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>7060 ANDRES AVELINO CACERES</t>
+          <t>7087 EL NAZARENO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.15274</t>
+          <t>896</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-76.96267</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>-12.13769</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.95633</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>330996</t>
+          <t>329832</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>L'HERMITAGE</t>
+          <t>7082 JUAN DE ESPINOSA MEDRANO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.15682</t>
+          <t>784</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-76.96774</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>-12.13264</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.96277</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>331694</t>
+          <t>329813</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HEROES DEL PACIFICO</t>
+          <t>7081 JOSE MARIA ARGUEDAS A</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.17175</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-76.96933</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>-12.17933</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.97971</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>688844</t>
+          <t>329808</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LATINO</t>
+          <t>7074 LA INMACULADA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-12.15994</t>
+          <t>762</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-76.98174</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>-12.137</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.96824</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>329714</t>
+          <t>329790</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>7041 VIRGEN DE LA MERCED</t>
+          <t>7070 DRA. MARIA REICHE GROSSE NEUMAN</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-12.16793</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-76.95869</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>-12.16776</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.97258</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>329766</t>
+          <t>329785</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>7063 ANDRES AVELINO CACERES</t>
+          <t>7069 CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-12.16747</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-76.97415</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>-12.15099</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.97448</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>331199</t>
+          <t>329771</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS</t>
+          <t>7067 TORIBIO SEMINARIO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-12.16039</t>
+          <t>606</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-76.97578</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>-12.15079</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.97775</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>329667</t>
+          <t>329766</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>7063 ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-12.15807</t>
+          <t>668</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-76.96832</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>-12.16747</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-76.97415</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>330562</t>
+          <t>329752</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SAN BARTOLOME</t>
+          <t>7062 NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-12.17285</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-76.96186</t>
+          <t>84</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>-12.15619</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-76.97483</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>330500</t>
+          <t>329747</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>7061 LOS HEROES DE SAN JUAN</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-12.18782</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-76.97432</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>-12.15593</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-76.97544</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>329851</t>
+          <t>329733</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>7099 HECTOR PRETELL / 7099 HECTOR PRETELL CARBONELL</t>
+          <t>7060 ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-12.17726</t>
+          <t>432</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-76.96907</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>-12.15274</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-76.96267</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>331439</t>
+          <t>329728</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AMERICA SIGLO XXI</t>
+          <t>7059 JOSE ANTONIO ENCINAS FRANCO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-12.18635</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-76.97633</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>-12.14751</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-76.96546</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>331910</t>
+          <t>329714</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LUZ Y ESPERANZA</t>
+          <t>7041 VIRGEN DE LA MERCED</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-12.1714</t>
+          <t>746</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-76.97004</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>-12.16793</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-76.95869</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>735807</t>
+          <t>329709</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>JESUS OBRERO DE OLLANTAY</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-12.13217</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-76.96347</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>-12.13536</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-76.95962</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>329342</t>
+          <t>329691</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>629-6034 CESAR CARBONEL RODRIGUEZ</t>
+          <t>6151 SAN LUIS GONZAGA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-12.14525</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-76.9757</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>-12.13945</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-76.97141</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>330524</t>
+          <t>329686</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>REVERENDO HERMANO GASTON MARIA</t>
+          <t>6096 ANTONIO RAIMONDI</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-12.1576</t>
+          <t>797</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-76.96416</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>-12.16712</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-76.96474</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>331731</t>
+          <t>329672</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SAN MARTINCITO DE PORRES</t>
+          <t>6089 JORGE BASADRE GROHMANN</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-12.13873</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-76.9641</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>-12.14668</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-76.96287</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>329686</t>
+          <t>329667</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>6096 ANTONIO RAIMONDI</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-12.16712</t>
+          <t>733</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-76.96474</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>-12.15807</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-76.96832</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>329771</t>
+          <t>329653</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>7067 TORIBIO SEMINARIO</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-12.15079</t>
+          <t>873</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-76.97775</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>-12.14849</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-76.97236</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>495746</t>
+          <t>329648</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 65</t>
+          <t>6045 DOLORES CAVERO DE GRAU</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-12.12732</t>
+          <t>827</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-76.94741</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>-12.15338</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-76.96729</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>329832</t>
+          <t>329634</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>7082 JUAN DE ESPINOSA MEDRANO</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-12.13264</t>
+          <t>949</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-76.96277</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>-12.1444</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-76.97127</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>330393</t>
+          <t>329610</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MI PEQUEÑO JARDIN</t>
+          <t>6037 INCA PACHACUTEC</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-12.15766</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-76.96829</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-12.15682</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-76.964</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>329653</t>
+          <t>329592</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>6037 INCA PACHACUTEC</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-12.14849</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-76.97236</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>-12.15624</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-76.96192</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,37 +4965,37 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>787009</t>
+          <t>329587</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ANNIE'S SCHOOL</t>
+          <t>652 27 LA MERCED DE LIMA / 7229 LA MERCED DE LIMA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-12.16241</t>
+          <t>276</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-76.96204</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>-12.18287</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-76.95871</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>331335</t>
+          <t>329549</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>NIÑO JESUS</t>
+          <t>652 19 HORACIO ZEBALLOS GAMEZ / 7227 HORACIO ZEBALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-12.15076</t>
+          <t>442</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-76.9701</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>-12.1408</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-76.97873</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>330519</t>
+          <t>329506</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ROSA DE SANTA MARIA</t>
+          <t>652 13 LOS TREBOLITOS</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-12.16351</t>
+          <t>193</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-76.97354</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>-12.17753</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-76.96367</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>329969</t>
+          <t>329498</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>JULIO CESAR ESCOBAR</t>
+          <t>652 12 VIRGEN DEL BUEN PASO</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-12.16274</t>
+          <t>335</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-76.9744</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>-12.14156</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-76.9625</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>329865</t>
+          <t>329484</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>7100 REPUBLICA ALEMANA</t>
+          <t>7223 MIGUEL COLINA MARIE</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-12.18017</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-76.95866</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>-12.15372</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-76.9797</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>329634</t>
+          <t>329422</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>638 PAMPAS DE SAN JUAN</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-12.1444</t>
+          <t>245</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-76.97127</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>-12.1668</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-76.96566</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>329808</t>
+          <t>329417</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>7074 LA INMACULADA</t>
+          <t>637 VALLE SHARON</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-12.137</t>
+          <t>447</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-76.96824</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>-12.17238</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-76.97072</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>329993</t>
+          <t>329399</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>635 EL UNIVERSO</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-12.1485</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-76.97524</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>-12.18626</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-76.95811</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5461,37 +5461,37 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>688580</t>
+          <t>329380</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>EMMANUEL COLLEGE</t>
+          <t>7219 ARISTOTELES</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-12.16197</t>
+          <t>245</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-76.96249</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-12.18595</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-76.95748</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>329648</t>
+          <t>329356</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>6045 DOLORES CAVERO DE GRAU</t>
+          <t>630 JUAN PABLO II</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-12.15338</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-76.96729</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>-12.1394</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-76.95698</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>329846</t>
+          <t>329342</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>7087 EL NAZARENO</t>
+          <t>629-6034 CESAR CARBONEL RODRIGUEZ</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-12.13769</t>
+          <t>674</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-76.95633</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>-12.14525</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-76.9757</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>329790</t>
+          <t>329337</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>7070 DRA. MARIA REICHE GROSSE NEUMAN</t>
+          <t>627 / 7212</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-12.16776</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-76.97258</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>-12.17348</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-76.96406</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5719,22 +5719,22 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
+          <t>1067</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
           <t>-12.18447</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>-76.97897</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1067</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>52</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>329610</t>
+          <t>329295</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>6037 INCA PACHACUTEC</t>
+          <t>559 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-12.15682</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-76.964</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>-12.17768</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-76.97801</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>329672</t>
+          <t>329281</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>6089 JORGE BASADRE GROHMANN</t>
+          <t>551</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-12.14668</t>
+          <t>269</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-76.96287</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>-12.13602</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-76.96065</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>329728</t>
+          <t>329276</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>7059 JOSE ANTONIO ENCINAS FRANCO</t>
+          <t>547 JESUS PODEROSO</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-12.14751</t>
+          <t>344</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-76.96546</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>-12.14829</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-76.98153</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>329747</t>
+          <t>329262</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>7061 LOS HEROES DE SAN JUAN</t>
+          <t>541 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-12.15593</t>
+          <t>343</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-76.97544</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>-12.13875</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-76.97184</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>330350</t>
+          <t>329257</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MARY'S CHILDREN SCHOOL</t>
+          <t>JESUS NIÑO</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-12.16094</t>
+          <t>453</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-76.96305</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>-12.16629</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-76.97278</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6081,32 +6081,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>329813</t>
+          <t>329243</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>7081 JOSE MARIA ARGUEDAS A</t>
+          <t>537 LOS LAURELES</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-12.17933</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-76.97971</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>-12.14733</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-76.96239</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6143,32 +6143,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>329691</t>
+          <t>329238</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>6151 SAN LUIS GONZAGA</t>
+          <t>530 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-12.13945</t>
+          <t>514</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-76.97141</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>-12.15953</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-76.96722</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6205,42 +6205,42 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>688575</t>
+          <t>329224</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>EMMANUEL COLLEGE</t>
+          <t>514 EL CARMEN</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-12.16215</t>
+          <t>421</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-76.96257</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-12.16368</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-76.97778</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>329785</t>
+          <t>329219</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>7069 CESAR VALLEJO</t>
+          <t>513 NIÑOS DE MARIA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-12.15099</t>
+          <t>268</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-76.97448</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>-12.16988</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>-76.97503</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>330171</t>
+          <t>329200</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FERMIN TANGUIS</t>
+          <t>66 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-12.1553</t>
+          <t>368</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-76.97698</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>-12.14809</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-76.97192</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>331745</t>
+          <t>329196</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 3</t>
+          <t>56 MI DULCE HOGAR</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-12.14995</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-76.96923</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>-12.15342</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>-76.96783</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>329752</t>
+          <t>329182</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>7062 NACIONES UNIDAS</t>
+          <t>46 MI JARDIN DE AMOR</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-12.15619</t>
+          <t>325</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-76.97483</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>-12.15124</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>-76.97361</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>329295</t>
+          <t>326763</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>559 SAGRADO CORAZON DE JESUS</t>
+          <t>CRISTO SEMBRADOR</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-12.17768</t>
+          <t>314</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-76.97801</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-12.13875</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.96307</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6577,32 +6577,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>329506</t>
+          <t>059104</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>652 13 LOS TREBOLITOS</t>
+          <t>LEONARD EULER II</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-12.17753</t>
+          <t>418</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-76.96367</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>-12.16352</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.97335</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-SAN_JUAN_DE_MIRAFLORES.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SAN_JUAN_DE_MIRAFLORES.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
